--- a/artfynd/A 35869-2023 artfynd.xlsx
+++ b/artfynd/A 35869-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 35869-2023 artfynd.xlsx
+++ b/artfynd/A 35869-2023 artfynd.xlsx
@@ -2022,7 +2022,7 @@
         <v>111523740</v>
       </c>
       <c r="B14" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 35869-2023 artfynd.xlsx
+++ b/artfynd/A 35869-2023 artfynd.xlsx
@@ -2022,7 +2022,7 @@
         <v>111523740</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
